--- a/outputs/M3_lagged_main_model_regression_detail.xlsx
+++ b/outputs/M3_lagged_main_model_regression_detail.xlsx
@@ -40,22 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct_lag1</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp_lag1</t>
+  </si>
+  <si>
+    <t>ln_gdppc_lag1</t>
+  </si>
+  <si>
+    <t>xr_dep_pct_lag1</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp_lag1</t>
   </si>
   <si>
     <t>deposit_interest_rate_pct_lag1</t>
-  </si>
-  <si>
-    <t>inflation_gdp_deflator_pct_lag1</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp_lag1</t>
-  </si>
-  <si>
-    <t>ln_gdppc_lag1</t>
-  </si>
-  <si>
-    <t>xr_dep_pct_lag1</t>
   </si>
 </sst>
 </file>
@@ -444,22 +444,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>-5.018919662956976</v>
+        <v>-5.018919662957058</v>
       </c>
       <c r="C2">
-        <v>27.43453840627884</v>
+        <v>27.43453840624873</v>
       </c>
       <c r="D2">
-        <v>-0.1829416478102039</v>
+        <v>-0.1829416478104076</v>
       </c>
       <c r="E2">
-        <v>0.8554046194481058</v>
+        <v>0.8554046194479463</v>
       </c>
       <c r="F2">
-        <v>-59.79374289531396</v>
+        <v>-59.79374289525393</v>
       </c>
       <c r="G2">
-        <v>49.75590356940001</v>
+        <v>49.75590356933981</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.05651646652260672</v>
+        <v>0.09999895890049132</v>
       </c>
       <c r="C3">
-        <v>0.06161514549981715</v>
+        <v>0.05484242980225108</v>
       </c>
       <c r="D3">
-        <v>0.9172495831041158</v>
+        <v>1.82338673288299</v>
       </c>
       <c r="E3">
-        <v>0.3623515884135544</v>
+        <v>0.07277347250714716</v>
       </c>
       <c r="F3">
-        <v>-0.06650214065089785</v>
+        <v>-0.009497485091573027</v>
       </c>
       <c r="G3">
-        <v>0.1795350736961113</v>
+        <v>0.2094954028925557</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.02413543465222104</v>
+        <v>-0.02195076498864351</v>
       </c>
       <c r="C4">
-        <v>0.4671950615948038</v>
+        <v>0.02917525942500034</v>
       </c>
       <c r="D4">
-        <v>-0.05166029488803457</v>
+        <v>-0.752376000119946</v>
       </c>
       <c r="E4">
-        <v>0.9589554131757616</v>
+        <v>0.4545000301923112</v>
       </c>
       <c r="F4">
-        <v>-0.9569204713426398</v>
+        <v>-0.08020104987030227</v>
       </c>
       <c r="G4">
-        <v>0.9086496020381978</v>
+        <v>0.03629951989301524</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.09999895890049135</v>
+        <v>0.7934007726236924</v>
       </c>
       <c r="C5">
-        <v>0.05484242980226879</v>
+        <v>3.034070045222437</v>
       </c>
       <c r="D5">
-        <v>1.823386732882402</v>
+        <v>0.2614971839140667</v>
       </c>
       <c r="E5">
-        <v>0.07277347250723731</v>
+        <v>0.794523448523087</v>
       </c>
       <c r="F5">
-        <v>-0.009497485091608374</v>
+        <v>-5.264315524276456</v>
       </c>
       <c r="G5">
-        <v>0.2094954028925911</v>
+        <v>6.85111706952384</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-0.02195076498864351</v>
+        <v>-0.0007344046440457609</v>
       </c>
       <c r="C6">
-        <v>0.02917525942499768</v>
+        <v>0.1090994756197773</v>
       </c>
       <c r="D6">
-        <v>-0.7523760001200147</v>
+        <v>-0.006731513968089409</v>
       </c>
       <c r="E6">
-        <v>0.4545000301922706</v>
+        <v>0.9946493752846779</v>
       </c>
       <c r="F6">
-        <v>-0.08020104987029694</v>
+        <v>-0.2185585357928483</v>
       </c>
       <c r="G6">
-        <v>0.03629951989300993</v>
+        <v>0.2170897265047568</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.7934007726236818</v>
+        <v>0.05651646652260663</v>
       </c>
       <c r="C7">
-        <v>3.03407004522573</v>
+        <v>0.06161514549981835</v>
       </c>
       <c r="D7">
-        <v>0.2614971839137795</v>
+        <v>0.9172495831040964</v>
       </c>
       <c r="E7">
-        <v>0.7945234485233075</v>
+        <v>0.3623515884135644</v>
       </c>
       <c r="F7">
-        <v>-5.264315524283041</v>
+        <v>-0.06650214065090033</v>
       </c>
       <c r="G7">
-        <v>6.851117069530404</v>
+        <v>0.1795350736961136</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.0007344046440459153</v>
+        <v>-0.02413543465222161</v>
       </c>
       <c r="C8">
-        <v>0.1090994756197708</v>
+        <v>0.4671950615947149</v>
       </c>
       <c r="D8">
-        <v>-0.006731513968091225</v>
+        <v>-0.05166029488804564</v>
       </c>
       <c r="E8">
-        <v>0.9946493752846766</v>
+        <v>0.9589554131757529</v>
       </c>
       <c r="F8">
-        <v>-0.2185585357928355</v>
+        <v>-0.9569204713424628</v>
       </c>
       <c r="G8">
-        <v>0.2170897265047436</v>
+        <v>0.9086496020380197</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M3_lagged_main_model_regression_detail.xlsx
+++ b/outputs/M3_lagged_main_model_regression_detail.xlsx
@@ -40,6 +40,12 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>broad_money_growth_pct_lag1</t>
+  </si>
+  <si>
+    <t>deposit_interest_rate_pct_lag1</t>
+  </si>
+  <si>
     <t>inflation_gdp_deflator_pct_lag1</t>
   </si>
   <si>
@@ -50,12 +56,6 @@
   </si>
   <si>
     <t>xr_dep_pct_lag1</t>
-  </si>
-  <si>
-    <t>broad_money_pct_gdp_lag1</t>
-  </si>
-  <si>
-    <t>deposit_interest_rate_pct_lag1</t>
   </si>
 </sst>
 </file>
@@ -444,22 +444,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>-5.018919662957058</v>
+        <v>-22.73507627259828</v>
       </c>
       <c r="C2">
-        <v>27.43453840624873</v>
+        <v>22.01672682240523</v>
       </c>
       <c r="D2">
-        <v>-0.1829416478104076</v>
+        <v>-1.032627440762994</v>
       </c>
       <c r="E2">
-        <v>0.8554046194479463</v>
+        <v>0.3040229340650522</v>
       </c>
       <c r="F2">
-        <v>-59.79374289525393</v>
+        <v>-66.36269024251081</v>
       </c>
       <c r="G2">
-        <v>49.75590356933981</v>
+        <v>20.89253769731424</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.09999895890049132</v>
+        <v>0.1223252832460348</v>
       </c>
       <c r="C3">
-        <v>0.05484242980225108</v>
+        <v>0.05719382775746545</v>
       </c>
       <c r="D3">
-        <v>1.82338673288299</v>
+        <v>2.138784691326554</v>
       </c>
       <c r="E3">
-        <v>0.07277347250714716</v>
+        <v>0.03464520919784353</v>
       </c>
       <c r="F3">
-        <v>-0.009497485091573027</v>
+        <v>0.008991895454480384</v>
       </c>
       <c r="G3">
-        <v>0.2094954028925557</v>
+        <v>0.2356586710375893</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.02195076498864351</v>
+        <v>0.1274492401803073</v>
       </c>
       <c r="C4">
-        <v>0.02917525942500034</v>
+        <v>0.1521201521417744</v>
       </c>
       <c r="D4">
-        <v>-0.752376000119946</v>
+        <v>0.8378195681892685</v>
       </c>
       <c r="E4">
-        <v>0.4545000301923112</v>
+        <v>0.4039324496088179</v>
       </c>
       <c r="F4">
-        <v>-0.08020104987030227</v>
+        <v>-0.1739869963783418</v>
       </c>
       <c r="G4">
-        <v>0.03629951989301524</v>
+        <v>0.4288854767389563</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.7934007726236924</v>
+        <v>-0.03219179431629284</v>
       </c>
       <c r="C5">
-        <v>3.034070045222437</v>
+        <v>0.04850460646601323</v>
       </c>
       <c r="D5">
-        <v>0.2614971839140667</v>
+        <v>-0.6636853004641809</v>
       </c>
       <c r="E5">
-        <v>0.794523448523087</v>
+        <v>0.5082678800456111</v>
       </c>
       <c r="F5">
-        <v>-5.264315524276456</v>
+        <v>-0.128306910052219</v>
       </c>
       <c r="G5">
-        <v>6.85111706952384</v>
+        <v>0.06392332141963328</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-0.0007344046440457609</v>
+        <v>-0.01699084476352753</v>
       </c>
       <c r="C6">
-        <v>0.1090994756197773</v>
+        <v>0.01975812905812862</v>
       </c>
       <c r="D6">
-        <v>-0.006731513968089409</v>
+        <v>-0.8599419870950482</v>
       </c>
       <c r="E6">
-        <v>0.9946493752846779</v>
+        <v>0.3916745294053814</v>
       </c>
       <c r="F6">
-        <v>-0.2185585357928483</v>
+        <v>-0.05614289648624482</v>
       </c>
       <c r="G6">
-        <v>0.2170897265047568</v>
+        <v>0.02216120695918975</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.05651646652260663</v>
+        <v>1.113059567839169</v>
       </c>
       <c r="C7">
-        <v>0.06161514549981835</v>
+        <v>0.8672081518957003</v>
       </c>
       <c r="D7">
-        <v>0.9172495831040964</v>
+        <v>1.283497584064497</v>
       </c>
       <c r="E7">
-        <v>0.3623515884135644</v>
+        <v>0.2019908529316981</v>
       </c>
       <c r="F7">
-        <v>-0.06650214065090033</v>
+        <v>-0.6053712773837019</v>
       </c>
       <c r="G7">
-        <v>0.1795350736961136</v>
+        <v>2.83149041306204</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.02413543465222161</v>
+        <v>0.0584508535092774</v>
       </c>
       <c r="C8">
-        <v>0.4671950615947149</v>
+        <v>0.04686674179689388</v>
       </c>
       <c r="D8">
-        <v>-0.05166029488804564</v>
+        <v>1.247171261927819</v>
       </c>
       <c r="E8">
-        <v>0.9589554131757529</v>
+        <v>0.2149597691907728</v>
       </c>
       <c r="F8">
-        <v>-0.9569204713424628</v>
+        <v>-0.03441872404580614</v>
       </c>
       <c r="G8">
-        <v>0.9086496020380197</v>
+        <v>0.1513204310643609</v>
       </c>
     </row>
   </sheetData>
